--- a/Sample_run/1/student/DuyCNHE187327/TC2/GradeDetail.xlsx
+++ b/Sample_run/1/student/DuyCNHE187327/TC2/GradeDetail.xlsx
@@ -1044,7 +1044,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1103,7 +1103,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1156,7 +1156,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1212,7 +1212,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>55</x:v>
@@ -1327,7 +1327,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>55</x:v>
@@ -1380,7 +1380,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1439,7 +1439,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>55</x:v>
@@ -1492,7 +1492,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1551,7 +1551,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>55</x:v>
@@ -1604,7 +1604,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>4000</x:v>
@@ -1663,7 +1663,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>35950</x:v>
+        <x:v>36272</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
         <x:v>55</x:v>
